--- a/src/attributions/attributions_ig_traj_371.xlsx
+++ b/src/attributions/attributions_ig_traj_371.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG9"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,79 +1568,79 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.0090453481775412</v>
+        <v>-0.1789969626281112</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3267211508159703</v>
+        <v>0.07660602402652766</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.199894649193821</v>
+        <v>-0.106245510892444</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05180688185451818</v>
+        <v>-0.1081161344625763</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1076902711389653</v>
+        <v>0.01883336545830946</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05259219311298755</v>
+        <v>-0.1798014916237575</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0296315911639291</v>
+        <v>-0.003899952013007181</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2111869237100639</v>
+        <v>0.07001980490943467</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1260031930036017</v>
+        <v>-0.06965504178722985</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
         <v>-0</v>
@@ -1649,130 +1649,130 @@
         <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.1115068032419464</v>
+        <v>0.08377786460653165</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.05659508641743188</v>
+        <v>-0.07631946520361935</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.06653387699598515</v>
+        <v>-0.1161143451902468</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.07561194201207087</v>
+        <v>0.02702393874563975</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.09036169060264229</v>
+        <v>-0.0998109296249589</v>
       </c>
       <c r="AN3" t="n">
         <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.09176782984015353</v>
+        <v>-0.1126636230575638</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.07338371336160071</v>
+        <v>-0.1107928071578447</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3704451829430171</v>
+        <v>-0.01965818368427522</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.6391349675816723</v>
+        <v>-0.3405096752227905</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.2094809407815305</v>
+        <v>-0.07699150825405861</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0632289188643569</v>
+        <v>0.04332769483183316</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.04573037833652644</v>
+        <v>0.180878284200614</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.1164571350735155</v>
+        <v>0.1526556364233778</v>
       </c>
       <c r="BM3" t="n">
         <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.2672403288223454</v>
+        <v>0.05532306331659931</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1528698885027471</v>
+        <v>0.008322216054234029</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
         <v>-0</v>
@@ -1784,22 +1784,22 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0187798147733362</v>
+        <v>-0.1228082723604679</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0806441891503888</v>
+        <v>0.09979093418496257</v>
       </c>
       <c r="BX3" t="n">
         <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2746127203775935</v>
+        <v>-0.1306937194521693</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
@@ -1811,52 +1811,52 @@
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.01157929673917106</v>
+        <v>0.09485319331608173</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.08460632656358688</v>
+        <v>0.01516987203759337</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.07644577851125711</v>
+        <v>0.08410286607529474</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
         <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.002207116618845708</v>
+        <v>-0.01552140183038544</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.07952371922509226</v>
+        <v>-0.0142412870480675</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.3063663642177141</v>
+        <v>-0.05335014871148709</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
         <v>-0</v>
@@ -1865,19 +1865,19 @@
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.03654204322660716</v>
+        <v>0.07859883935532415</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.05226157307386584</v>
+        <v>-0.008669548634967871</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.01272636207927349</v>
+        <v>0.04342840520657793</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
@@ -1892,100 +1892,100 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.01846041797466224</v>
+        <v>0.01297903775922754</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.003262691618200415</v>
+        <v>0.0001552021619890967</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.1727192543397875</v>
+        <v>0.1543506280498649</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.1802326493696176</v>
+        <v>0.07882200433647256</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.07064079279879214</v>
+        <v>0.07969895459409002</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.09134422570865458</v>
+        <v>-0.08605134911061324</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.06983166556525749</v>
+        <v>-0.02703388514028469</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.0582891044609129</v>
+        <v>0.1954242832666221</v>
       </c>
       <c r="DZ3" t="n">
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0385673072968061</v>
+        <v>-0.1263795324990779</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.08189134840541497</v>
+        <v>0.05679509224590104</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.1496428269313499</v>
+        <v>0.04241970904095305</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.01136360982056992</v>
+        <v>0.06796264823733185</v>
       </c>
       <c r="EK3" t="n">
         <v>-0</v>
@@ -1994,79 +1994,79 @@
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.1497517768104901</v>
+        <v>0.02756014476870844</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0008444259313419785</v>
+        <v>0.03153573866408805</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.13203198661705</v>
+        <v>0.09291614987194266</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.06165017774570217</v>
+        <v>0.07946476037302423</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.06570765422236877</v>
+        <v>-0.02680192240145657</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.02288434871876048</v>
+        <v>0.06298501932501346</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
         <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0.01713130383939527</v>
+        <v>0.2719037818177438</v>
       </c>
       <c r="FH3" t="n">
         <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0.01551284156985115</v>
+        <v>0.05385976904325497</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.06205644345365041</v>
+        <v>-0.01911261098729578</v>
       </c>
       <c r="FL3" t="n">
         <v>-0</v>
@@ -2075,31 +2075,31 @@
         <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.04780172514080363</v>
+        <v>0.2240485932185003</v>
       </c>
       <c r="FQ3" t="n">
         <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0.001008579917184531</v>
+        <v>0.002470622464825584</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.005418480358399515</v>
+        <v>0.005373537166437742</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
         <v>0</v>
@@ -2108,13 +2108,13 @@
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.08318611979306738</v>
+        <v>0.1692839721755936</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0.01277263618891139</v>
+        <v>0.03873219209223326</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
@@ -2123,16 +2123,16 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6768547304271948</v>
+        <v>0.5956126568002915</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.286352289118672</v>
+        <v>-0.3071601632807637</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1572337397667257</v>
+        <v>-0.1272143434271992</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,25 +2161,25 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4000489838352853</v>
+        <v>0.4748508231284136</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1809381852557439</v>
+        <v>-0.2863264417476739</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.135737063351224</v>
+        <v>-0.1434590501240533</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -2191,28 +2191,28 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2091093647303794</v>
+        <v>0.1176752697786788</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.003121113636187528</v>
+        <v>-0.1014551369887247</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07058301184889663</v>
+        <v>-0.09270849089913381</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -2221,22 +2221,22 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.138588226021961</v>
+        <v>-0.05224821521548723</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.01168628018018015</v>
+        <v>-0.1075421295186243</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1030890316647367</v>
+        <v>-0.1269964436062522</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2245,28 +2245,28 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1382524299557517</v>
+        <v>0.2749540833204451</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.06196927746032804</v>
+        <v>-0.1461467617536752</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.04966302105649899</v>
+        <v>0.1489147172881272</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,43 +2275,43 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.6834439056102668</v>
+        <v>0.5843006098612095</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.1148174927171546</v>
+        <v>-0.215704642651913</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1407785318081522</v>
+        <v>-0.3324736848142719</v>
       </c>
       <c r="AY4" t="n">
         <v>-0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.06738376610247729</v>
+        <v>-0.06201660276980012</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.05901730541784217</v>
+        <v>-0.1066411937670286</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.324408259333705</v>
+        <v>-0.09687062555634814</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.06110532394069219</v>
+        <v>-0.04706783887710865</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1526789837577328</v>
+        <v>0.06378613665538875</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.005724864735483472</v>
+        <v>0.07001867130931187</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,25 +2356,25 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.2477078766374605</v>
+        <v>0.3489276013525644</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.02627702766125847</v>
+        <v>-0.1414292217894174</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.01527091564263937</v>
+        <v>-0.06855336778525099</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,19 +2383,19 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.1316840947931531</v>
+        <v>-0.2218357636303399</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.04078026446858752</v>
+        <v>0.2163629336434455</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.02425205047534399</v>
+        <v>0.02290235057649759</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ4" t="n">
         <v>-0</v>
@@ -2404,79 +2404,79 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.02268175633215287</v>
+        <v>-0.2137558454871064</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.1238867453722931</v>
+        <v>0.2350004921579852</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1571066124498058</v>
+        <v>0.1341620197160028</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.1108361786274455</v>
+        <v>-0.2202507004218109</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.08296334301595341</v>
+        <v>0.2343904117451779</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.0383657673161363</v>
+        <v>0.03885818028049465</v>
       </c>
       <c r="DA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.09188089226902638</v>
+        <v>-0.1324547388194176</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.007252551859755759</v>
+        <v>-0.01385143772057836</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0007557587384421496</v>
+        <v>0.003461337424368055</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.1220717293003114</v>
+        <v>-0.1377795021662583</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.003663887757100351</v>
+        <v>0.08023123565056661</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.07233411565370992</v>
+        <v>-0.03575753023320501</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
@@ -2518,22 +2518,22 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.06778435159974187</v>
+        <v>0.02905721993814226</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.05518597998873514</v>
+        <v>0.07873621136354633</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.08705432056987654</v>
+        <v>0.02301911720240868</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
         <v>0</v>
@@ -2545,49 +2545,49 @@
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.02316076053072037</v>
+        <v>-0.1832667718217544</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.1280521251562182</v>
+        <v>0.1688543306762482</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.001403937451307096</v>
+        <v>0.05788174327203558</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
         <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.1061742812758056</v>
+        <v>-0.1245597862444739</v>
       </c>
       <c r="EQ4" t="n">
         <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.04555293691704249</v>
+        <v>-0.166241671515401</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.05526206294222665</v>
+        <v>-0.01635266842082285</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,46 +2599,46 @@
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.1204212204884043</v>
+        <v>-0.2521082832488822</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.07388869568611921</v>
+        <v>0.2460968297654943</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.0453350077744332</v>
+        <v>0.01364393865614593</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.01286076708782778</v>
+        <v>-0.1515846730952072</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.1290941937101929</v>
+        <v>0.1384640018181922</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.002318283039130152</v>
+        <v>0.03051110338647128</v>
       </c>
       <c r="FL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.01212586042940261</v>
+        <v>0.005973552420983917</v>
       </c>
       <c r="FR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.03136558576053207</v>
+        <v>0.2161163844630275</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0005543344477491443</v>
+        <v>-0.001771273719864695</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2677,39 +2677,39 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.01635086112183172</v>
+        <v>-0.2058410573385716</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.04637275783324324</v>
+        <v>0.1132157099225872</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1613306227257895</v>
+        <v>0.5066892816592586</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1341233859793937</v>
+        <v>-0.09103808328127927</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.05206950766302488</v>
+        <v>-0.2315884853815701</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
@@ -2736,22 +2736,22 @@
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08703925317253709</v>
+        <v>0.4860147192108515</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.09648764721718332</v>
+        <v>-0.1739747789597319</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.03080768875337093</v>
+        <v>-0.1128164378672203</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2760,52 +2760,52 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03133708062881857</v>
+        <v>0.1452124812419135</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01790072166518056</v>
+        <v>-0.1893664020604323</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04715693511830685</v>
+        <v>-0.02721446853691462</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.03296068417845219</v>
+        <v>0.02374052061303864</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01150732923792172</v>
+        <v>-0.2774418787164495</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01917364283519599</v>
+        <v>0.06684038254111899</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
@@ -2814,25 +2814,25 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.04226980504410863</v>
+        <v>0.128684152800777</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.02742056457177104</v>
+        <v>-0.05695596396698766</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.02447719139080726</v>
+        <v>-0.08908993050051936</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2841,28 +2841,28 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1493690405057131</v>
+        <v>0.6537060812394138</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.08324225401359364</v>
+        <v>-0.3279534715761419</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.02437616027368288</v>
+        <v>-0.2379254222075513</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.04321487706621466</v>
+        <v>-0.02707214700955962</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,52 +2880,52 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.07518399607585963</v>
+        <v>-0.0765247260501954</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.01975031571027485</v>
+        <v>-0.04991965515558354</v>
       </c>
       <c r="BI5" t="n">
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.06238754774141839</v>
+        <v>0.07582283795207595</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02989903458715408</v>
+        <v>0.1368022858401409</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.02981453767522116</v>
+        <v>0.0499917190990263</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0652727654804541</v>
+        <v>0.3194579089779624</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,25 +2934,25 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.02716616622320389</v>
+        <v>-0.1048570105236069</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.01870397940777774</v>
+        <v>-0.07903099199289573</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.02802423383846431</v>
+        <v>-0.1824924815836163</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
@@ -2961,118 +2961,118 @@
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.02481967082115658</v>
+        <v>0.05489273154647441</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01909478112492195</v>
+        <v>0.09401596642759819</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01598849575591904</v>
+        <v>-0.2479055382057017</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.008067701072107344</v>
+        <v>0.226091283343882</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.02500136876545432</v>
+        <v>0.06325126445802312</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.01569100674384484</v>
+        <v>-0.1641422239350127</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.02394521694234303</v>
+        <v>0.04315793100375621</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.02549341328257096</v>
+        <v>0.100780688094986</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.01232750948820411</v>
+        <v>-0.04296268854482148</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01208410911799054</v>
+        <v>-0.08690075297558762</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.00443659838226281</v>
+        <v>0.02432046750017627</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.02060192418467505</v>
+        <v>-0.09304915448242811</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01554347662904607</v>
+        <v>0.00290966780914791</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.03773747965928601</v>
+        <v>0.03441781178564522</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
@@ -3087,76 +3087,76 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.005006861812670466</v>
+        <v>0.06923539403469096</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03343845592505647</v>
+        <v>-0.1109589786942062</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.02939942520309967</v>
+        <v>-0.006548869929047103</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.01883254255267887</v>
+        <v>-0.07615042344253171</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.02317394284058918</v>
+        <v>-0.03284262586401593</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01258489604281309</v>
+        <v>0.06378463684079184</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.01662538978101152</v>
+        <v>-0.05535981843433195</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.01851308672418978</v>
+        <v>-0.08474767425803756</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.03159573958968867</v>
+        <v>0.1407104827067018</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3168,25 +3168,25 @@
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.01386687733282042</v>
+        <v>-0.1930189674403001</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.02094706520193713</v>
+        <v>0.03080335391053342</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.02762722303772199</v>
+        <v>0.08414849154931994</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
@@ -3195,34 +3195,34 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.03235791348486353</v>
+        <v>-0.1519547329873583</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.03193102132322991</v>
+        <v>0.05806991615226062</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01849185157563376</v>
+        <v>0.1263120255686063</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001537571304812677</v>
+        <v>0.01912231125799166</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
@@ -3231,43 +3231,43 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.001784221538342116</v>
+        <v>-0.009722037375552795</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.005180230722711923</v>
+        <v>0.0854519345685248</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02820141911724529</v>
+        <v>-0.1220049564230292</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.02662506825605961</v>
+        <v>0.04696755491062164</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3844,103 +3844,103 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.3535265906337405</v>
+        <v>0.7427732382935295</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2859339868834381</v>
+        <v>-0.1165949370443221</v>
       </c>
       <c r="E7" t="n">
-        <v>0.274883573759541</v>
+        <v>-0.3938842165940645</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1932753326272808</v>
+        <v>0.6311897138182092</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1947304908104412</v>
+        <v>-0.3463418338386953</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2932928065889529</v>
+        <v>-0.5501284334292523</v>
       </c>
       <c r="O7" t="n">
         <v>-0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1307148232942271</v>
+        <v>-0.01502948595258967</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.08475879881400032</v>
+        <v>-0.1654401735081841</v>
       </c>
       <c r="W7" t="n">
-        <v>0.09525274671552875</v>
+        <v>-0.05556030254277627</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
         <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.08825618915868277</v>
+        <v>0.1598176058589894</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.04641461857072769</v>
+        <v>-0.1012960738267766</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.00392420985748522</v>
+        <v>-0.1391596163777023</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -3952,100 +3952,100 @@
         <v>-0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0916634066377479</v>
+        <v>0.405782156672298</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.0002458037700372174</v>
+        <v>-0.1913461331361342</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.1214267207028675</v>
+        <v>0.1727621182353586</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.4714263727842218</v>
+        <v>0.6449315555319155</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1051221789130924</v>
+        <v>-0.09718681013014896</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.02517026163759578</v>
+        <v>-0.2954287990849582</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.01253181331995625</v>
+        <v>0.1038678698733916</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.04234061603064319</v>
+        <v>-0.03116623672608318</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.308736518295445</v>
+        <v>-0.2332943438197382</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.1148918777185862</v>
+        <v>-0.002190081380827783</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.05163510551234789</v>
+        <v>0.02479414994928107</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.1011918004277744</v>
+        <v>0.1586571911276359</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
@@ -4057,130 +4057,130 @@
         <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.1902679126559514</v>
+        <v>0.3586359884722489</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02140220870435444</v>
+        <v>-0.2164153342446777</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1110534148836139</v>
+        <v>-0.07965266988197374</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>-0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0756969421288666</v>
+        <v>-0.3493274972512919</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.02423423022391335</v>
+        <v>0.09251323200208354</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02727126711307931</v>
+        <v>-0.001876463759026401</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="n">
         <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02258479801504088</v>
+        <v>-0.3031991144498747</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0908075751501934</v>
+        <v>0.2637067972340125</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.03087184064703569</v>
+        <v>-0.02231744239192713</v>
       </c>
       <c r="CR7" t="n">
         <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU7" t="n">
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.05296510659849454</v>
+        <v>-0.3307248316291947</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.04673312941921113</v>
+        <v>0.10066947395648</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02298846337139623</v>
+        <v>0.02855220188607864</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.047664738579144</v>
+        <v>-0.1338834029820987</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.002390803233928819</v>
+        <v>-0.008782310102553995</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.001704049653533248</v>
+        <v>-0.03997384951592865</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,82 +4189,82 @@
         <v>-0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.1177564158006951</v>
+        <v>-0.234804109389837</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.0568588803121003</v>
+        <v>0.05344049575706696</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.03471474836137795</v>
+        <v>0.04898770035462247</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.02470304738239621</v>
+        <v>0.04098374355042003</v>
       </c>
       <c r="DY7" t="n">
         <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.05609361646616716</v>
+        <v>0.1845553569491247</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.05743837303411233</v>
+        <v>0.4061285219933906</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.05936317556627226</v>
+        <v>-0.1974999971065492</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.0660364129726157</v>
+        <v>0.02384640633524717</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.01576657985571617</v>
+        <v>-0.03215045319728884</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
@@ -4279,100 +4279,100 @@
         <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.05409245926369587</v>
+        <v>-0.2015931304082794</v>
       </c>
       <c r="EQ7" t="n">
         <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.04148467880954274</v>
+        <v>0.06658185195095455</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.03406421907139789</v>
+        <v>0.08287622141626166</v>
       </c>
       <c r="ET7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
         <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.049944682094452</v>
+        <v>-0.3959727120804108</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.04448200587875669</v>
+        <v>0.1020154607484453</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03129880808709181</v>
+        <v>-0.006055485236270379</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
         <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.009943701954090306</v>
+        <v>-0.2954604012950897</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.1232345382660162</v>
+        <v>0.1459223713531193</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.03678731109232182</v>
+        <v>0.2544802878189198</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.00717207470794921</v>
+        <v>0.0891332724460228</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.03056483655090257</v>
+        <v>0.2760193931681877</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.04328019973158977</v>
+        <v>0.01588684617998121</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
         <v>0</v>
@@ -4381,25 +4381,25 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY7" t="n">
         <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.01559193438758244</v>
+        <v>-0.09039149281959556</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.06045052855016572</v>
+        <v>-0.1309761595309228</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE7" t="n">
         <v>0</v>
@@ -4413,19 +4413,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>1.479973266844613</v>
+        <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.366721057858814</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08532578762152405</v>
+        <v>-0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -4434,25 +4434,25 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.174669328845304</v>
+        <v>-0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.322662037711207</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1784802153789106</v>
+        <v>-0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4467,22 +4467,22 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1666280167650273</v>
+        <v>-0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.07856006950843873</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.003427647439567487</v>
+        <v>-0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -4494,22 +4494,22 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2211429020684371</v>
+        <v>-0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.1997263770688445</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1004107561632006</v>
+        <v>-0</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -4521,103 +4521,103 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.2052548836783624</v>
+        <v>-0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.092462756424667</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.008237632099742733</v>
+        <v>-0</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.9735903055764584</v>
+        <v>-0</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.4227595029101938</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1350112976285543</v>
+        <v>-0</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.4817417945926575</v>
+        <v>-0</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.5123795329078787</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.2199596716232918</v>
+        <v>-0</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1933257529662728</v>
+        <v>-0</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>-0.3261970174058931</v>
+        <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.3141687696844003</v>
+        <v>-0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
@@ -4626,25 +4626,25 @@
         <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.5295731603208662</v>
+        <v>-0</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.1865443356073932</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.1945096156651563</v>
+        <v>-0</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
@@ -4659,22 +4659,22 @@
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.2392728099404783</v>
+        <v>-0</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.2435078455920171</v>
+        <v>0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.05063580752064673</v>
+        <v>-0</v>
       </c>
       <c r="CI8" t="n">
         <v>0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,25 +4686,25 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.1713669146719727</v>
+        <v>-0</v>
       </c>
       <c r="CO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.01274584424961466</v>
+        <v>0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.05119496832474154</v>
+        <v>-0</v>
       </c>
       <c r="CR8" t="n">
         <v>0</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>0</v>
@@ -4713,46 +4713,46 @@
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.21514503859233</v>
+        <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.2504944643347122</v>
+        <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.02287500042119803</v>
+        <v>0</v>
       </c>
       <c r="DA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.6730368904003899</v>
+        <v>-0</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.2563979950308195</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.007693586736755487</v>
+        <v>-0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4764,22 +4764,22 @@
         <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.1347658881819185</v>
+        <v>-0</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.09032750604579859</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.03293503449243314</v>
+        <v>-0</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
@@ -4794,16 +4794,16 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.1482336751397358</v>
+        <v>0</v>
       </c>
       <c r="DY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.1393074142315704</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.09817154537767148</v>
+        <v>0</v>
       </c>
       <c r="EB8" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
@@ -4821,76 +4821,76 @@
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.1939880596378885</v>
+        <v>-0</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0.100668331733528</v>
+        <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.09727862652724481</v>
+        <v>-0</v>
       </c>
       <c r="EK8" t="n">
         <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.1394628679287139</v>
+        <v>-0</v>
       </c>
       <c r="EQ8" t="n">
         <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.2264799170701719</v>
+        <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.004866124451873613</v>
+        <v>-0</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.227709409968083</v>
+        <v>-0</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.2192750679983748</v>
+        <v>0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.03754913129438246</v>
+        <v>-0</v>
       </c>
       <c r="FC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
@@ -4902,43 +4902,43 @@
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.03807351423942956</v>
+        <v>-0</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.1065447895731372</v>
+        <v>0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.1393887309658001</v>
+        <v>-0</v>
       </c>
       <c r="FL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
         <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP8" t="n">
         <v>0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.1303505153741816</v>
+        <v>0</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>-0.06297747978449567</v>
+        <v>0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.1025965675498607</v>
+        <v>0</v>
       </c>
       <c r="FU8" t="n">
         <v>0</v>
@@ -4956,48 +4956,48 @@
         <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.06790225707878805</v>
+        <v>0</v>
       </c>
       <c r="GA8" t="n">
         <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.1171282692665396</v>
+        <v>0</v>
       </c>
       <c r="GC8" t="n">
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF8" t="n">
         <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.4359815246301266</v>
+        <v>0.3878730388940006</v>
       </c>
       <c r="C9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4718761791829003</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1156876976204974</v>
+        <v>-0.0001612508713251405</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>-0.2873459930576874</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
@@ -5009,76 +5009,76 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3415869383224051</v>
+        <v>0.4454571660890848</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5267068366026778</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05178230849345734</v>
+        <v>-0.07466373481244883</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>-0.1281998719840469</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06282174319583683</v>
+        <v>0.1015788779632274</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.05676147070284845</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.05609452362594246</v>
+        <v>-0.1147834687677106</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.004578205098268082</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>-0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.1661720702045666</v>
+        <v>-0.01351668225221736</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0123532719661941</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.0996462220535201</v>
+        <v>-0.2966197082070361</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0.06002517494941146</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -5093,19 +5093,19 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.0537101822278517</v>
+        <v>0.1406958833703736</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.07487764565707392</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.02291920950299189</v>
+        <v>-0.03619187086660465</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0</v>
+        <v>-0.09037953385610799</v>
       </c>
       <c r="AQ9" t="n">
         <v>-0</v>
@@ -5114,28 +5114,28 @@
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.2254365194076659</v>
+        <v>0.6300223187738523</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.1815176571864835</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.1162848109312128</v>
+        <v>-0.2011817873483422</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>-0.1248753335926902</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -5147,19 +5147,19 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.1901658304067562</v>
+        <v>-0.02613853201256226</v>
       </c>
       <c r="BE9" t="n">
         <v>-0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.1977482601154656</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.1064275149806939</v>
+        <v>-0.1448066351944176</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0</v>
+        <v>-0.1518106446033877</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
@@ -5174,22 +5174,22 @@
         <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.02214472635467394</v>
+        <v>0.0498612041680769</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0504806852493777</v>
+        <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.07040462918400971</v>
+        <v>0.1071114107784503</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>0.04883607747103749</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
@@ -5198,49 +5198,49 @@
         <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.06575159976274975</v>
+        <v>0.2679470648008238</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.1171529889953752</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.1324334334542377</v>
+        <v>-0.04217763132867423</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>-0.07469168968583779</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.06745654294723229</v>
+        <v>-0.143995689605884</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.1165091156783931</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.04812156296191444</v>
+        <v>0.01832007806976258</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0.1073150134596358</v>
       </c>
       <c r="CJ9" t="n">
         <v>0</v>
@@ -5249,109 +5249,109 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.02185985076007273</v>
+        <v>-0.1822162946240146</v>
       </c>
       <c r="CO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.09634130602196353</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.03714203642667075</v>
+        <v>0.2121635092464745</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0</v>
+        <v>0.0760974165502666</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.09010157542025901</v>
+        <v>-0.1320163996636272</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0.1023476109536826</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.02169321857981353</v>
+        <v>0.0007733726945896921</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0.1128304205897249</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.09330774394366353</v>
+        <v>-0.08387702268720751</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0.003884068459489228</v>
+        <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01752444979467531</v>
+        <v>-0.1142518075558335</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>0.04467224927793573</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
         <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.02491417302721137</v>
+        <v>-0.09899172760415433</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.03005318400664825</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.001729606560937753</v>
+        <v>0.001394003426171459</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0</v>
+        <v>0.07570239795200423</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5360,22 +5360,22 @@
         <v>-0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.1187634119193375</v>
+        <v>0.02820825510005134</v>
       </c>
       <c r="DY9" t="n">
         <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.07731852250270733</v>
+        <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.1114669988529639</v>
+        <v>-0.03063170492303592</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0</v>
+        <v>0.02496051888305572</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
@@ -5390,19 +5390,19 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.03291938864316571</v>
+        <v>-0.0497665135034675</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0.07376220343285665</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.009902926332031974</v>
+        <v>-0.02636059232325923</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0.0441566236378042</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
@@ -5411,28 +5411,28 @@
         <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.09352644547294127</v>
+        <v>-0.04084410390877706</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.0007959602556867462</v>
+        <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.06113806617484525</v>
+        <v>-0.1159265315671437</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>-0.1673800329880761</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5441,22 +5441,22 @@
         <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.1057497010977716</v>
+        <v>-0.165083942683934</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0.08410533273550594</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0379463692057752</v>
+        <v>0.0009663542194615714</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0</v>
+        <v>0.1021138865786065</v>
       </c>
       <c r="FD9" t="n">
         <v>0</v>
@@ -5468,76 +5468,76 @@
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.003868613226928485</v>
+        <v>-0.1437305274487897</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.06584904689199719</v>
+        <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.004410617585389942</v>
+        <v>0.1077182294172834</v>
       </c>
       <c r="FL9" t="n">
-        <v>0</v>
+        <v>0.03543254066597465</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.05749160532360922</v>
+        <v>0.03372467894513073</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.06102109519008222</v>
+        <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.06434173330481482</v>
+        <v>-0.03859899093807414</v>
       </c>
       <c r="FU9" t="n">
-        <v>0</v>
+        <v>0.03581889078892852</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.02280704780793221</v>
+        <v>-0.05224698203394884</v>
       </c>
       <c r="GA9" t="n">
         <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.2246034725071126</v>
+        <v>-0</v>
       </c>
       <c r="GC9" t="n">
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0</v>
+        <v>0.04311287594122956</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
@@ -5546,6 +5546,3420 @@
         <v>-0</v>
       </c>
       <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.4416740373767888</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1292815850088376</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1722232136180434</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.4103832174106081</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2226383344417559</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2274601434723344</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.06687202702216012</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.07723771093349303</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.005348629773740201</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.06894447909571907</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.1002754680237976</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.02340032299440625</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.284938428958599</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.06622705927231855</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.2832419984912994</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.2664861018752087</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.1167032726042174</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.1727773468689827</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.0273602751262169</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.04661760774502691</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.2604658648484377</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.1682725717985085</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.08203811923356261</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.07351550969426607</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0.4210844459828117</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.1348118848515209</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0.01798600266071378</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.2938382160279187</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0.06192790764516205</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.02041745797669618</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.1579765724838858</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0.1603009802893139</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0.08976736031365548</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.2863276378628508</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-0.05422802254216771</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.003342077614450956</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0.2173465765833407</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>-0.04337864471672342</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.06657359309022146</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0.1304340548034429</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>-0.1175486628514845</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.02006755864840289</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>-0.1104775631050581</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>-0.09164350398499459</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>-0.2389694319804792</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0.2298560346404862</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0.01613528068130857</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0.03684097176490068</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0.175708154744508</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>-0.05927384589239611</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.03679101536798692</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0.3204046225374293</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>-0.08228990976353238</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.003881954064293794</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.176931901050265</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>-0.06249282325533757</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0.1288608595907365</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0.1256667800033877</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0.1973908710519009</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.01397516333576579</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.1980529491009003</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>-0.0175132327562679</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.3798866793551395</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.05600073928736143</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.2020981413000932</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.4033803489769109</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.05561169955784798</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.1943078748261784</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.09568750310640917</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.0154202939275363</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.003023951178904337</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.02506812420469167</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.08290493178155231</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.01334718592030236</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.07626816406219065</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.04730141301345846</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.04302296890540561</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.3903730912672635</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.1490591281903597</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.1026196989162462</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.03813574507916682</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.01148184849259375</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-0.08481107196756277</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.0535899533287896</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.09176301331672394</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.04377552499291766</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.228603254937176</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.005657642581431398</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>-0.09415744739936156</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-0.1273078487660538</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0.003807178566061563</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.08398848456256482</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-0.02726292711759027</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.04561248425870312</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.02542157500130647</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-0.1197913801620914</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.01123557372949002</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.1022527119353458</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.03554119877606568</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-0.06170293488512844</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.04594569811736698</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>-0.0142525086498161</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0.07753866980008624</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0.08613922527750111</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>-0.0995440774652628</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.008189954048393547</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.01514724689214075</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>-0.05258966043225227</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>-0.05752938664133046</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.04430423464834197</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.02228131317312769</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0.02476373403261649</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.004633313890826024</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>-0.1364723883120243</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0.03622041669556148</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.0759118745010874</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>-0.1219646196567499</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.002411032990650409</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.1262655876398902</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>-0.1873025186888818</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.02014240126949313</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.06776962469886105</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>-0.03721070658620606</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.03202336555508709</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.3719604183209871</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1185219353106485</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.08495175259493068</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.3535704304963105</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2223888694128998</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1809408276419006</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.05091499261448269</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.02520704741253559</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.02007795375375419</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.0831118867763133</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.1463684423030133</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.2031962240345859</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.1884946105686173</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.02172800061271427</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.2353734118616539</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-0.259094310943167</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.1149536952256766</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.04546326743474729</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.008355251407211942</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.05259891839500178</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.1267969693966313</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.09761950168557203</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.09974103883957806</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-0.01175616770563958</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-0.2077286858400209</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0.06893265157821733</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.01194895883860823</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.2136457397793112</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0.0526364824822646</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.0107595282998769</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.08839639812039345</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0.1665314697123023</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>-0.0492945211697222</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0.2167165485159334</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>-0.06379689334304886</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.03201155573669698</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.04739257722633586</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0.03759830111001793</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>-0.02514430572354225</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.1441212617724332</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>-0.02550729842073712</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0.01343847102285133</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.04708336719978088</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>0.04061904417783251</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>-0.01758288060734572</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>0.2316085845041906</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0.07571893133005772</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.02334384043331988</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>-0.1360432162531141</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0.0166620412646013</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.001223132591818316</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>0.2529573703020898</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0.07153774011112304</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.01189368505071449</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>0.06018010502582839</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>0.08887350821374346</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.07455853047682837</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>0.1922878232634816</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>0.04231881068615078</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>-0.03603896309901711</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>0.1931776969137755</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0.0005143310865827681</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3801088972054176</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.04818642399111507</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1798506566783235</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.4610684728781204</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.1696703044227142</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.1829136314240734</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.1039148241784596</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.1309589418394732</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.02107537039665941</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.04409458364326283</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.2434886783125185</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.05222276966429916</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.02543793646756181</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.05898588718151545</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.01249612865721162</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.4523409942324362</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.2990900906957171</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.1575608202950972</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.02753018179058724</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0.0209940414613752</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0.06415306399553877</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.06909843563840605</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.08994881124424943</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0.0003881153621909424</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.245090031865229</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.08552600451148583</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0.09024615094745193</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.1134838087901542</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.03541674155894555</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.06108018626721665</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.1222546075558408</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.1461117943977293</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.1008026497155244</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.1160957673814095</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.02195847313047311</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.08156258904384492</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.04268285818389663</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.1796604745616948</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.02232689619676888</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-0.01220985861684473</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>-0.08645613389516908</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.0677045797034778</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0.003148464091676574</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>-0.01828436807170635</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.02799535032659593</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>-0.05237578834196016</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.02090085115677771</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.004164192437540469</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.01808400212864439</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.002191816098393776</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.1193651947181323</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>-0.129568384628751</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.008592599785250482</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.0498054022852524</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.2040567145334455</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>-0.08188854312610831</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.1390628393984205</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.07705834592034287</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>-0.1284002253646416</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>-0.06122044274965908</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0.03382413365858077</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.07891776144269004</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3856514504487089</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.4562662713261113</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.1536898236134784</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.3383707284177859</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.4729834782718894</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.3250574976450354</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.08736234896041828</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.07595159366311915</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1699733308242269</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.008397951867511541</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.1437963118652451</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.1448540280904759</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.2075816658284972</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.1776199529016932</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.03746936664940437</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.3727787513087217</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0.2875663487961226</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.5215505838595809</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.03128794280887706</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-0.1128392372261139</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.1091727033925911</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.1320743490922999</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.2167011719738545</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.06384011818871992</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.280955312057036</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>-0.2503229699761909</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.1725820117129377</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.09689081973458977</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.2705347851895755</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.05164336934342995</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.05879794412175526</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.3099403819247418</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.1024029483312167</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.08190559392306022</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.2867844537770141</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.08797001751065442</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.1147762496721865</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-0.02838579905533811</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.1137091986571816</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.1340595864249777</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.03455776017000221</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.05481794687705103</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.06089973287973872</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.1591713784207479</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>-0.06844226057019974</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.0260024241681069</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0.2258192898622783</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.05633080143614799</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.0547485832847505</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0.2157092825584848</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.01664871347770657</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.1160327003954715</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.3137748331831855</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.0403671353551274</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.1111189800532998</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.1953455800613784</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0.03938578411769555</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.02710895688739692</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.2684925370818458</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>-0.1103626442292858</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.04876948506823624</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0.1767882816069995</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.519022922561875</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.04488917344854914</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.4105766495212397</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.6654138328127865</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.1939852693957323</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.4075856123662687</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.1372558331358201</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.1089876666283394</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.07526516950782365</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.06072661086096562</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.2872931023524127</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.1092863644479519</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.1226161936504729</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.04169800516754105</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.08293182041590805</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.6613005964513121</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.3098130189458019</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.3231699491754152</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.08987412160099394</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.03600861380320628</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-0.03951130407414213</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.1353120086430671</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.06682611310305893</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.07097490846572901</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.3680927948356272</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.08497610960758817</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-0.1739796582338521</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.1507293068311164</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.06528069184648301</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.10255606487947</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.2410148877635986</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.2038675699011357</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.01835065156460425</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.1461425269646365</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.04218041845793669</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.14300995251582</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0.0141541018239467</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0.1313584930767523</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.03412429633329329</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0.08621199339201918</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0.02270572054919769</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.126388790600333</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0.06365576649596101</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0.01376483542926447</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0.03950653164157924</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.03616040904807231</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0.01448161302290622</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0.0232300577009319</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0.03271359594397874</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0.09104750924947981</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.008363811133862078</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.1730037905874527</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.01479052126298267</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.1200034910501969</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.1463316581504215</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0.07562989318443324</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.1833463528764804</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0.05274860118369525</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>-0.1268261806644628</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>-0.1454615709017769</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>-0.01899540438444769</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.1925126419714358</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG15" t="n">
         <v>0</v>
       </c>
     </row>
